--- a/Dataset/example_sheet.xlsx
+++ b/Dataset/example_sheet.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_Articles" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset_example" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo_example" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo_Quick_example" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legal_Update_2025" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -524,7 +524,6 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Dataset/example_sheet.xlsx
+++ b/Dataset/example_sheet.xlsx
@@ -524,6 +524,11 @@
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ví dụ minh hoạ — điền dữ liệu thật khi dùng</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,37 +552,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>question_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>question_vi</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>expected_answer_vi</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>article_reference</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ground_truth_rule</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>question_type</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>split</t>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>retrieval_keywords</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>expected_retrieved_context</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>evaluation_focus</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
@@ -589,37 +624,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>factual</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>công ty trách nhiệm hữu hạn một thành viên</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Công ty TNHH một thành viên là gì?</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Là doanh nghiệp do một tổ chức hoặc một cá nhân làm chủ sở hữu; chủ sở hữu chịu trách nhiệm về các khoản nợ trong phạm vi số vốn điều lệ.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Điều 4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Công ty TNHH một thành viên do một chủ sở hữu, chịu trách nhiệm hữu hạn trong phạm vi vốn điều lệ.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>factual</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>demo</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>công ty TNHH một thành viên;chủ sở hữu;trách nhiệm hữu hạn</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Điều 4. Công ty TNHH một thành viên là doanh nghiệp do một tổ chức hoặc một cá nhân làm chủ sở hữu; chủ sở hữu công ty chịu trách nhiệm về các khoản nợ và nghĩa vụ tài sản khác của công ty trong phạm vi số vốn điều lệ.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>định nghĩa loại hình doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Ví dụ minh hoạ — điền dữ liệu thật khi dùng</t>
         </is>
       </c>
     </row>
@@ -631,37 +696,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>quyền thành lập doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Ai có quyền thành lập doanh nghiệp?</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Mọi tổ chức, cá nhân đều có quyền thành lập và quản lý doanh nghiệp, trừ các trường hợp bị pháp luật cấm.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Điều 17</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Quyền thành lập doanh nghiệp là quyền chung, trừ trường hợp bị cấm.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>test</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>quyền thành lập;điều kiện thành lập;cấm thành lập</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Điều 17. Tổ chức, cá nhân có quyền thành lập và quản lý doanh nghiệp, trừ các trường hợp bị cấm theo quy định của pháp luật.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>điều kiện/chủ thể có quyền thành lập</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ví dụ minh hoạ — điền dữ liệu thật khi dùng</t>
         </is>
       </c>
     </row>
@@ -676,7 +771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,37 +782,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>question_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>question_vi</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>expected_answer_vi</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>article_reference</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ground_truth_rule</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>question_type</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>split</t>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>retrieval_keywords</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>expected_retrieved_context</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>evaluation_focus</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
@@ -729,37 +854,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>factual</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>công ty trách nhiệm hữu hạn một thành viên</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Công ty TNHH một thành viên là gì?</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Là doanh nghiệp do một tổ chức hoặc một cá nhân làm chủ sở hữu; chủ sở hữu chịu trách nhiệm về các khoản nợ trong phạm vi số vốn điều lệ.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Điều 4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Công ty TNHH một thành viên do một chủ sở hữu, chịu trách nhiệm hữu hạn trong phạm vi vốn điều lệ.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>factual</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>easy</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>demo</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>công ty TNHH một thành viên;chủ sở hữu;trách nhiệm hữu hạn</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Điều 4. Công ty TNHH một thành viên là doanh nghiệp do một tổ chức hoặc một cá nhân làm chủ sở hữu; chủ sở hữu công ty chịu trách nhiệm về các khoản nợ và nghĩa vụ tài sản khác của công ty trong phạm vi số vốn điều lệ.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>định nghĩa loại hình doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Ví dụ minh hoạ — điền dữ liệu thật khi dùng</t>
         </is>
       </c>
     </row>
@@ -774,50 +929,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>article_reference</t>
+          <t>update_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>topic</t>
+          <t>date/effective</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>legal_source</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>key_change_vi</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>impact_on_dataset</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>implemented_in_sheet</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Điều 17</t>
+          <t>UPD001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mở rộng quyền thành lập doanh nghiệp</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bổ sung một số trường hợp được miễn hạn chế thành lập doanh nghiệp so với luật cũ.</t>
+          <t>Luật Doanh nghiệp 2020</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>Mở rộng quyền thành lập doanh nghiệp — bổ sung một số trường hợp được miễn hạn chế thành lập doanh nghiệp so với luật cũ.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cập nhật Điều 17 trong Dataset_example, Demo_Quick_example.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Dataset_example; Demo_Quick_example</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ví dụ minh hoạ — điền dữ liệu thật khi dùng</t>
         </is>
       </c>
     </row>

--- a/Dataset/example_sheet.xlsx
+++ b/Dataset/example_sheet.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KB_Articles" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,13 +20,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,13 +54,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -128,7 +134,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -171,71 +177,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -243,7 +191,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -266,7 +214,7 @@
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -357,7 +305,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -379,11 +327,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
+          <a:path path="circle"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -398,15 +344,12 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:path path="circle"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -416,7 +359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,10 +390,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>so_ky_hieu</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -484,10 +432,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>59/2020/QH14</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Ví dụ minh hoạ — điền dữ liệu thật khi dùng</t>
         </is>
@@ -521,12 +474,59 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>59/2020/QH14</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Ví dụ minh hoạ — điền dữ liệu thật khi dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Điều 52 Nghị định 168/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Thông báo thay đổi thông tin chủ sở hữu hưởng lợi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp thông báo trong thời hạn 10 ngày khi có thay đổi thông tin chủ sở hữu hưởng lợi hoặc tỷ lệ sở hữu đã kê khai.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>thay đổi chủ sở hữu hưởng lợi;10 ngày;công ty cổ phần</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>decree=168; article=52; type=beneficial_owner_change</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>168/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://xaydungchinhsach.chinhphu.vn/toan-van-nghi-dinh-168-2025-nd-cp-ve-dang-ky-doanh-nghiep-119250702175708554.htm</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VD văn bản khác Luật Doanh nghiệp 2020 — điền đúng so_ky_hieu thực tế của văn bản</t>
         </is>
       </c>
     </row>
@@ -538,8 +538,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -761,15 +761,17 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -919,7 +921,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 
@@ -929,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,10 +969,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>so_ky_hieu</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1007,10 +1016,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>59/2020/QH14</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=147025</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Ví dụ minh hoạ — điền dữ liệu thật khi dùng</t>
         </is>
